--- a/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
+++ b/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -659,7 +660,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Efectivo / valores bursátiles</t>
+          <t>Efectivo (numerario) / valores bursátiles cotizados en custodia</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -767,7 +768,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Bancarizados con soporte</t>
+          <t>Bancarizados con soporte (ahorros, dividendos, salarios, etc.)</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -821,7 +822,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Sin desviación / no evaluable</t>
+          <t>Opera conforme al contrato / aún no evaluado</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1178,6 +1179,222 @@
       <c r="E27" s="6" t="inlineStr">
         <is>
           <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>UbicacionPatrimonio</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ubic</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Estado donde está el bien (nivel de la tabla F7 del banco), «Bien en el extranjero» o «No aplica…».</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Bien en Jalisco</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>ClienteBanco</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SI / NO</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · El integrante es cliente del banco: activa la ruta heredada.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PuntajeBanco</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Número 100–500</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Puntaje del cliente en CIFRE.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Precarga</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SI / NO</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Registro precargado desde la base CIFRE (pendiente de captura).</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CuentasCIFRE</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Informativo (precarga).</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BandaCIFRE</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>A / B / C</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Informativo (precarga).</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ListasCIFRE</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Valor del campo de listas en CIFRE; no invalida hasta confirmar su significado.</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FechaCIFRE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>AAAA-MM-DD</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>v1.9 · Fecha de la corrida de calificación.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>AE</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1576,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Efectivo / valores bursátiles</t>
+          <t>Efectivo (numerario) / valores bursátiles cotizados en custodia</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -1379,7 +1596,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>Bancarizados con soporte</t>
+          <t>Bancarizados con soporte (ahorros, dividendos, salarios, etc.)</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr">
@@ -1389,7 +1606,7 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>Sin desviación / no evaluable</t>
+          <t>Opera conforme al contrato / aún no evaluado</t>
         </is>
       </c>
       <c r="K2" s="10" t="inlineStr">
@@ -1476,7 +1693,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Efectivo / valores bursátiles</t>
+          <t>Efectivo (numerario) / valores bursátiles cotizados en custodia</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -1496,7 +1713,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>Bancarizados con soporte</t>
+          <t>Bancarizados con soporte (ahorros, dividendos, salarios, etc.)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -1506,7 +1723,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Sin desviación / no evaluable</t>
+          <t>Opera conforme al contrato / aún no evaluado</t>
         </is>
       </c>
       <c r="K3" s="10" t="inlineStr">
@@ -1752,7 +1969,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>Efectivo / valores bursátiles</t>
+          <t>Efectivo (numerario) / valores bursátiles cotizados en custodia</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -1772,7 +1989,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>Bancarizados con soporte</t>
+          <t>Bancarizados con soporte (ahorros, dividendos, salarios, etc.)</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -1782,7 +1999,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>Sin desviación / no evaluable</t>
+          <t>Opera conforme al contrato / aún no evaluado</t>
         </is>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -1829,7 +2046,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Inmuebles</t>
+          <t>Inmuebles y bienes muebles (vehículos, arte, joyas, maquinaria)</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -1849,7 +2066,7 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Venta de activos documentada</t>
+          <t>Venta de activos documentada (inmuebles, acciones, etc.)</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
@@ -1859,7 +2076,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Operaciones atípicas vs. fin</t>
+          <t>Operaciones poco usuales para el fin del contrato</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -1901,12 +2118,12 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Testamentario</t>
+          <t>Testamentario / planeación patrimonial</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Mixto (efectivo y especie)</t>
+          <t>Mixto (efectivo en numerario + especie)</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -1936,12 +2153,12 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Operaciones fuera del objeto</t>
+          <t>Operaciones fuera del objeto del contrato</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>Tercero / garante</t>
+          <t>Tercero administrador / garante / depositario</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -1983,7 +2200,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Acciones / partes sociales</t>
+          <t>Acciones, partes sociales y otros títulos no cotizados</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -2045,7 +2262,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Derechos de cobro / otros bienes</t>
+          <t>Derechos (de cobro, fideicomisarios, etc.) / otros bienes</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2092,7 +2309,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Público / gubernamental</t>
+          <t>Recibido por sustitución fiduciaria</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -2186,7 +2403,7 @@
     <row r="11">
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Efectivo intensivo</t>
+          <t>Alto manejo de efectivo (casas de empeño, gasolineras, restaurantes, menudeo)</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -2219,7 +2436,7 @@
     <row r="15">
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>Manejo intensivo de efectivo</t>
+          <t>Alto manejo de efectivo (casas de empeño, gasolineras, restaurantes, menudeo)</t>
         </is>
       </c>
     </row>
